--- a/products.xlsx
+++ b/products.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saraswatmajumder/Desktop/LIVE TRACKER/price-tracker-bot/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{154FC8B0-122F-3A44-B7BA-19F440BBD1FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5E92B05-125E-8449-8292-A924F027520E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" activeTab="1" xr2:uid="{2E971475-875F-4985-9108-799ACF574EE3}"/>
+    <workbookView xWindow="1480" yWindow="620" windowWidth="27320" windowHeight="17380" activeTab="1" xr2:uid="{2E971475-875F-4985-9108-799ACF574EE3}"/>
   </bookViews>
   <sheets>
     <sheet name="Cimexis Products" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="240">
   <si>
     <t>Brand Name</t>
   </si>
@@ -205,179 +205,563 @@
     <t>Honey and Lemon Soap</t>
   </si>
   <si>
-    <t>Product</t>
-  </si>
-  <si>
     <t>Hero Ingredient</t>
   </si>
   <si>
-    <t>SCP Link</t>
-  </si>
-  <si>
-    <t>Aloe Vera, Neem</t>
-  </si>
-  <si>
-    <t>Alite Active Neem &amp; Aloe Vera Soap</t>
-  </si>
-  <si>
     <t>Amazon</t>
   </si>
   <si>
-    <t>https://www.amazon.in/Cleanse-Natural-Protection-Hydration-Refreshed/dp/B0DNF54WB1/ref=sr_1_2_sspa?crid=1KH12Y9SG8OIN&amp;dib=eyJ2IjoiMSJ9.Iwh0-03nxc_1RvtDc0hQ4gumLXDqdVUIhJRp8Wz--3DzBI4S0tJ2OebvR_wWripVjyW7u3eflgSpJCcTtno14ojMUfi883DS397EfrOmKwUIo9PVPAmhB-NvgcHpDp5fkeboGNyzuYrk5moG-fmbJJGyrc-A-Ek8RtM2xIZqrhYeDwoAsn3o0qmiN4UPa79CXsu0FOsaoRNRQInRnfkHn_7-MfgSCGfJh2E7p1LdOeubYebJARuMF6G6wiX1o-O6GUQU1oTHHfg1-QTyObuVxRxhXgyGHoaDM9S9N1drRUE.Q16g2USIdRzicbqek9FsZ0FtlznnL2eyArs6eebfuZs&amp;dib_tag=se&amp;keywords=aloe%2Bvera%2Bneem%2Bsoap&amp;qid=1770440771&amp;sprefix=aloe%2Bvera%2Bnee%2Bsoap%2Caps%2C533&amp;sr=8-2-spons&amp;aref=nNldu59BBf&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1</t>
-  </si>
-  <si>
-    <t>Jivtara Neem &amp; Aloe Vera Ayurvedic Soap</t>
-  </si>
-  <si>
-    <t>https://www.amazon.in/JIVTARA-Neem-Aloe-Vera-Ayurvedic/dp/B0FRSH67NR/ref=sr_1_8?crid=1KH12Y9SG8OIN&amp;dib=eyJ2IjoiMSJ9.Iwh0-03nxc_1RvtDc0hQ4gumLXDqdVUIhJRp8Wz--3DzBI4S0tJ2OebvR_wWripVjyW7u3eflgSpJCcTtno14ojMUfi883DS397EfrOmKwUIo9PVPAmhB-NvgcHpDp5fkeboGNyzuYrk5moG-fmbJJGyrc-A-Ek8RtM2xIZqrhYeDwoAsn3o0qmiN4UPa79CXsu0FOsaoRNRQInRnfkHn_7-MfgSCGfJh2E7p1LdOeubYebJARuMF6G6wiX1o-O6GUQU1oTHHfg1-QTyObuVxRxhXgyGHoaDM9S9N1drRUE.Q16g2USIdRzicbqek9FsZ0FtlznnL2eyArs6eebfuZs&amp;dib_tag=se&amp;keywords=aloe+vera+neem+soap&amp;qid=1770440771&amp;sprefix=aloe+vera+nee+soap%2Caps%2C533&amp;sr=8-8</t>
-  </si>
-  <si>
-    <t>Glamova Neem &amp; Aloe Vera Bathing Soap</t>
-  </si>
-  <si>
-    <t>https://www.amazon.in/Neem-Aloe-Nourishing-Anti-Aging-Younger-Looking/dp/B0GGZ7VFQY/ref=sr_1_2_sspa?crid=VPIRKYRAJFJO&amp;dib=eyJ2IjoiMSJ9.9uHpevtJsPOCTBp8e1y2EEhgLYHAp2E5VCHHstWg7cGYof6pn9SIq7Xw19C2pB2df-yi3MrJ083iC71UOfEqzpK-52ew9V3wNJ320Lzy-nCI7q2G6xgLpPht8CCCqzL7OkNl4W-B9cV1LdM7-x9M54luvSyFIhffDyi6DmotRN2a8s7x3bqkHAnrXA8uRREQRkxDglWWb70Ct3wCltmhnOoqiaJnYoz-3dFfpU-V4J7G4PYzjsI5GdgbSr4YjH5JcCRmzQAbUNyRt23SnSVDDzwJuYXuhzUlyBAuIg_1cYg.3_hp__FC6apmrrawqCesUU72SkbjBKGUTrrUE6j18ls&amp;dib_tag=se&amp;keywords=aloe%2Bvera%2Bneem%2Bsoap&amp;qid=1770440895&amp;s=beauty&amp;sprefix=aloe%2Bvera%2Bneem%2Bsoap%2Cbeauty%2C353&amp;sr=1-2-spons&amp;aref=BOLlnmOWjQ&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1</t>
-  </si>
-  <si>
-    <t>Aloe Vera, Lavender</t>
-  </si>
-  <si>
-    <t>Selhphira Aloe Vera Ayurvedic Cleansing Bar</t>
-  </si>
-  <si>
-    <t>https://www.amazon.in/Selphira-Ayurvedic-Cleansing-Treatment-Hydration/dp/B0DP1BKLKQ?th=1</t>
-  </si>
-  <si>
-    <t>Naturable Aloe Vera Lavender Soap</t>
-  </si>
-  <si>
-    <t>https://www.amazon.in/Naturalable-Aloe-Lavender-Soap-100gms/dp/B08NSDS7BD</t>
-  </si>
-  <si>
-    <t>D Tan Soap</t>
-  </si>
-  <si>
-    <t>Turmeric, Multani Mitti, Sandalwood, Glycerine</t>
-  </si>
-  <si>
-    <t>Bombay Shaving Company De-Tan Bath Soap</t>
-  </si>
-  <si>
-    <t>Official Website</t>
-  </si>
-  <si>
-    <t>https://www.bombayshavingcompany.com/products/de-tan-bath-soap</t>
-  </si>
-  <si>
-    <t>Deshailly Tan Remover Soap</t>
-  </si>
-  <si>
-    <t>Brand Website</t>
-  </si>
-  <si>
-    <t>https://www.deshaillys.com/products/tan-remover-soap</t>
-  </si>
-  <si>
-    <t>Bright &amp; Beyond De-Tan Soap</t>
-  </si>
-  <si>
-    <t>https://brightandbeyond.in/product/de-tan-soap/</t>
-  </si>
-  <si>
-    <t>Neem, Charcoal, Glycerine</t>
-  </si>
-  <si>
-    <t>Brown Living Neem Charcoal Soap</t>
-  </si>
-  <si>
-    <t>https://brownliving.in/products/neem-bar-soap-for-all-skin-types-with-neem-oil-charcoal</t>
-  </si>
-  <si>
-    <t>Bijbel Khalkho Charcoal Soap</t>
-  </si>
-  <si>
-    <t>Meesho</t>
-  </si>
-  <si>
-    <t>https://www.meesho.com/charcoal-soap/p/8zz4ts</t>
-  </si>
-  <si>
-    <t>AuraBlush Charcoal Soap</t>
-  </si>
-  <si>
-    <t>https://www.meesho.com/charcoal-soap/p/bhtp7t</t>
-  </si>
-  <si>
-    <t>Chandan, Kesar, Glycerine</t>
-  </si>
-  <si>
-    <t>PrakritPurity Haldi Chandan Kesar Soap</t>
-  </si>
-  <si>
-    <t>https://prakritpurity.com/products/haldi-chandan-kesar-handmade-glycerin-soap</t>
-  </si>
-  <si>
-    <t>Brown Living Haldi Chandan Kesar Soap</t>
-  </si>
-  <si>
-    <t>https://brownliving.in/products/haldi-chandan-kesar-cold-process-handmade-soap-1</t>
-  </si>
-  <si>
-    <t>Raj Nature Trove Chandan Kesar Soap</t>
-  </si>
-  <si>
-    <t>https://rajnaturetrove.com/product/soap/</t>
-  </si>
-  <si>
-    <t>Activated Charcoal, Glycerine</t>
-  </si>
-  <si>
-    <t>The Man Company Charcoal &amp; Coconut Soap</t>
-  </si>
-  <si>
-    <t>https://www.themancompany.com/products/charcoal-soap-charcoal-coconut</t>
-  </si>
-  <si>
-    <t>TNW Charcoal Soap</t>
-  </si>
-  <si>
-    <t>Snapdeal</t>
-  </si>
-  <si>
-    <t>https://www.snapdeal.com/product/tnw-the-natural-wash-charcoal/620562715651</t>
-  </si>
-  <si>
-    <t>Advik Ayurveda Charcoal Tea Tree Soap</t>
-  </si>
-  <si>
-    <t>https://advikayurveda.com/charcoal-tea-tree-handmade-soap</t>
-  </si>
-  <si>
-    <t>TruBasic</t>
-  </si>
-  <si>
-    <t>AloeVera Neem Soap</t>
-  </si>
-  <si>
-    <t>AloeVera Lavender Neem Soap</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Similar Competitior Products (SCP) </t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCP Platform </t>
-  </si>
-  <si>
-    <t xml:space="preserve">SCP Pack Size </t>
+    <t>SKU Name</t>
+  </si>
+  <si>
+    <t>URL</t>
+  </si>
+  <si>
+    <t>Flipkart</t>
+  </si>
+  <si>
+    <t>Others (Meesho &amp; JioMart)</t>
+  </si>
+  <si>
+    <t>TruBasic AloeVera Neem</t>
+  </si>
+  <si>
+    <t>Neem &amp; Aloe Vera</t>
+  </si>
+  <si>
+    <t>1. Hamam Soap</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Bathing-NATURAL-INGREDIENTS-Healthy-Protected/dp/B08B8QN595/ref=sr_1_2?crid=2XEXYKJDXIGA&amp;dib=eyJ2IjoiMSJ9.qk-oVGoFvtAo5-GidcmW6bF2vZbNZGR7w5n_p8Pn1_krfNMDX4kPaueOjC5dSbcO6XxthUDzyar8Yg6p4zxcB2DAjXCVf-h42v8TJqtfR_t_zYd0KfB74dw8lfmCZCzyQbYiOAdDjJdNxxvMJJqd9zl0xYSy4QB_yvPuQR9MWPREKYftdREO7d9wl9UaoeUgfSnK06u6qh-fK1RjnnQxXscH-N677Zm64GuNvD9CiS5cY2M9a69OfwVqq4L1etHUZAuLIo0jEz2hle35xKPAnZxzNCUjhQxHKZyF_DPCgxs.BTPuUzoUWbZFyNHoVBcWTY_6YvxgiYpLW6L-vVjBz6A&amp;dib_tag=se&amp;keywords=hamam%2Bneed%2Band%2Baloe%2Bvera&amp;qid=1772344506&amp;sprefix=hamam%2Bneed%2Band%2Baloe%2Bve%2Caps%2C359&amp;sr=8-2&amp;th=1</t>
+  </si>
+  <si>
+    <t>1. Vivel Aloe/Vit E:  (Bestseller)</t>
+  </si>
+  <si>
+    <t>https://www.flipkart.com/vivel-aloe-vera-bathing-soap-vitamin-e-soft-skin-150g-each-women-men/p/itma49619325dddf?pid=SOPHYR84EYBMMQAG&amp;lid=LSTSOPHYR84EYBMMQAGOPRUJM&amp;marketplace=FLIPKART&amp;q=vivel+aloe+vera+vitamin+e+soap&amp;store=g9b%2F5nz%2Fb1b%2Fyug&amp;spotlightTagId=default_BestsellerId_g9b%2F5nz%2Fb1b%2Fyug&amp;srno=s_1_1&amp;otracker=search&amp;otracker1=search&amp;fm=Search&amp;iid=ff3e3d19-bc8a-4108-96c1-fe01c88a3a51.SOPHYR84EYBMMQAG.SEARCH&amp;ppt=sp&amp;ppn=sp&amp;ssid=meoua9oycg0000001772546484532&amp;qH=4a024958a7936de1&amp;ov_redirect=true&amp;ov_redirect=true</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Hamam (P3): 2k+ </t>
+  </si>
+  <si>
+    <t>https://blinkit.com/prn/hamam-neem-tulsi-and-aloe-vera-soap-pack-of-3/prid/263693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Meesho (Subaxo): 31 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Margo Neem: 6k+ </t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Margo-Original-Neem-Soap-125-Pack/dp/B082GB1N7K/ref=sr_1_1_in_f3_0o_fs_mod_primary_alm?crid=2AD2IV3L14352&amp;dib=eyJ2IjoiMSJ9.X0R0pGQXxWxn_fSQ2NztU_4B3h9HGaaYogcsAn_UfA-GOb1iYbEc4Am5vfiyuhRA4DpMT8QgDJCyCa2pcwuafScsgP4a1bAKe3fEjCS-4hJ2OnRjlKwO5VYK-58ajrWwUvkJUtSNHLCFa1Lu9Wn8Cl2bkojiPkpooZftyK96xsZKzGnJXr5n6etJHsqXIUzvdh_n_HL0ATPsAprJMqLyW8_t8QuT_8C0eC1fca7W7LB4_uFAd3oaLfFdz0ht2oDEo9TzvL6QBjpkw5hMlpP_StlPr7AWWk6M-LxovFkbLvQ.ARpWsKZjm9RZV5l_uLdRZBfaSQwA4nVpRT4JTHNEYV4&amp;dib_tag=se&amp;keywords=margo+neem&amp;qid=1772344780&amp;sbo=m6DjfpMzMLDmL8pSMKX8hw%3D%3D&amp;sprefix=margo+ne%2Caps%2C370&amp;sr=8-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. AAWAD Classic: 203 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Margo Neem: 1k+ </t>
+  </si>
+  <si>
+    <t>https://blinkit.com/prn/margo-neem-soap-5-x-100-g/prid/108028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. JioMart (Hamam): 1k+ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Himalaya Neem: 4k+ </t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Himalaya-Herbals-Turmeric-125gm-Value/dp/B011C1B2XY/ref=sr_1_1?crid=3I5F4AGWONCD3&amp;dib=eyJ2IjoiMSJ9.RU6lQbdyrqhbKuW26KvxsUcoRwU8dXdZah3ztKr-Pn6Fd58P9mSuAerZCb6yuqTrO2i-NETN2evH1FLwuM8r_47Iww-NoQhIBIqdk2cqyQEHYb7JA5XqDkjwB2msJQMO6ZAN_yCSelWTJPZni3IcxZrxGO6Fc9IkyhMN2NFxMhgIUsWViPHfi2q-JiKmQkPMzEzcea2NvBitb4y8OFJ8ynhBMnfTH1TzT43jZvf980ND5bWPdJtS-qjiI6WEWeEgmeMf3V6wNb8eVZ3VYMQoQBUcLhpNgkaDtesPYDU7wes.wZqkMbcgo3v68ubavr4c7PCbjz6-rDDcDvirAHoEJoc&amp;dib_tag=se&amp;keywords=himalaya+neem+soap&amp;qid=1772546441&amp;sprefix=himalaya+neem+a+soap%2Caps%2C364&amp;sr=8-1</t>
+  </si>
+  <si>
+    <t>3. Ayouthveda: (High visibility)</t>
+  </si>
+  <si>
+    <t>https://www.flipkart.com/ayouthveda-aloe-vera-bathing-soap/p/itm40e8c6189894b?pid=SOPGNPA2QARFYGZV&amp;lid=LSTSOPGNPA2QARFYGZVGVHSGG&amp;marketplace=FLIPKART&amp;q=ayouthveda+neem+aloevera+soap&amp;store=g9b%2F5nz%2Fb1b%2Fyug&amp;srno=s_1_2&amp;otracker=search&amp;otracker1=search&amp;fm=Search&amp;iid=en_aE4mlwoZsX3oJq4xbHAIGNWCgbv3E4UERzGAryXRzaDHrsSCLGEBBYZxcqaaPxcWqO6YDb7zvjhejqBK3itU6w%3D%3D&amp;ppt=sp&amp;ppn=sp&amp;qH=760000486eb14466&amp;ov_redirect=true&amp;ov_redirect=true</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Dettol Neem: 2k+ </t>
+  </si>
+  <si>
+    <t>https://blinkit.com/prn/dettol-neem-bathing-bar-buy-3-get-1-free/prid/496492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. JioMart (Austro): 4 </t>
+  </si>
+  <si>
+    <t>TruBasic AloeVera Lavender Neem</t>
+  </si>
+  <si>
+    <t>Lavender Oil</t>
+  </si>
+  <si>
+    <t>1. Yardley English Lavender: 531 , 4.4  (15k+ )</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Yardley-English-Lavender-Soap-Pack/dp/B00S857CUU/ref=sr_1_5?crid=RWAIHS2UIB5W&amp;dib=eyJ2IjoiMSJ9.yfzZHN7g-OjJKq57NYvO2RpOBwvSSxBt1IPRVR_ZQ5oY8gWHS_xBD4sV8ORh469FhXZBf2Hfp_gOi1I_25ywEzaah3VJ48N_bsa8wsSkaiEp6m9JbOEfeJ6MfriiBP4IVEp0Caf1VQaRAGSEGnz5NVKYqwHrjlr7uh7SRy0hEWyBERxZ1iHjKNzINvFByFu2wajv0yeY5LpYjhg-lssENw0QtQyTLH2dszT3f0a4yrOCCxU35QqQcfa5H_ykpPHXG6OG_HTbzJPkhZm8dz5D004G-EcAmkiI3wP21aAOMcs.T34NACrQyOlCRvU6fJas5K0Cv7lHcs9viTlC_oNxHYA&amp;dib_tag=se&amp;keywords=yardley+english+lavender+soaps&amp;qid=1772555255&amp;sprefix=yardley+english+laven%2Caps%2C373&amp;sr=8-5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Yardley Luxury: 83 , 4.2 </t>
+  </si>
+  <si>
+    <t>https://www.flipkart.com/yardley-london-english-lavender-90-naturally-derived-daily-bathing-luxury-soap-women/p/itm0fc388db1559c?pid=SOPEU6NPU9MYJFMS&amp;lid=LSTSOPEU6NPU9MYJFMSETQQHW&amp;marketplace=FLIPKART&amp;q=yardley+luxury+soap&amp;store=g9b%2F5nz%2Fb1b%2Fyug&amp;srno=s_1_2&amp;otracker=search&amp;otracker1=search&amp;fm=Search&amp;iid=177dacc7-1a06-4fd3-bceb-2e35901c841c.SOPEU6NPU9MYJFMS.SEARCH&amp;ppt=sp&amp;ppn=sp&amp;ssid=qj91hzqmkg0000001772555554054&amp;qH=ab1717523daf7c78&amp;ov_redirect=true&amp;ov_redirect=true</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Yardley London: 450+ , 4.4 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Meesho (Globus): 150 , 3.8 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Khadi Organic: 1k+ , 4.1 </t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Khadi-Natural-Pure-Lavender-Soap/dp/B014CPOEDW/ref=sr_1_1?crid=1FT95KD3Z4PWC&amp;dib=eyJ2IjoiMSJ9.lDh-XFttC-klGF4NY6al353kOcDdKxsBrC1GHU782gHMSMFlS38gZ_3F_DzhjCZjGXqqBEJEZ8TwNkCu3taUoDTozT_HllhxTec8UT5JpZlC3YBiHLCICJO5PVyAKkzO-UC9sWH8cJ-yaLfjDlFk95rdNBpYOzly7b2w6Y0OBAdIkt8RqpXB9H6cp68dvkFaoH0TtbEB5ozzmZ_IYnViPU-3c0zU0hWDi9HoAMgtVxu6FMbggRV7oINX_Pl5dD1DEQVh7RUp0_Fs57-6SWkTOvTVh13V0sTdrt0AJ7W0LYU.WLhyLeGL1gqmYEQbMnO3mpNS6wnnt4dcOnf91ggx5Dc&amp;dib_tag=se&amp;keywords=khadi+organic+lavender+soap&amp;qid=1772555327&amp;sprefix=khadi+organic+lavender+so%2Caps%2C367&amp;sr=8-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Soulflower Lavender: 102 , 4.0 </t>
+  </si>
+  <si>
+    <t>https://www.flipkart.com/soulflower-skin-lavender-moisturizing-handmade-soap-acne-blemish-control-your/p/itmc2083ec2273a5?pid=SOPETG6CQNVHWSK8&amp;lid=LSTSOPETG6CQNVHWSK8HPPJOZ&amp;marketplace=FLIPKART&amp;q=soulflower+lavender+soap&amp;store=g9b%2F5nz%2Fb1b%2Fyug&amp;srno=s_1_3&amp;otracker=search&amp;otracker1=search&amp;fm=Search&amp;iid=96338666-1a13-4d5e-a94b-af697584fe07.SOPETG6CQNVHWSK8.SEARCH&amp;ppt=sp&amp;ppn=sp&amp;ssid=ywmxkjdx1s0000001772555639105&amp;qH=f06110c470713549&amp;ov_redirect=true&amp;ov_redirect=true</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Pears Soft &amp; Fresh: 800+ , 4.5 </t>
+  </si>
+  <si>
+    <t>https://blinkit.com/prn/pears-soft-fresh-soap-buy-3-get-1-free/prid/362297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Meesho (Ayush): 6 , 4.0 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Mysore Sandal Lavender: 96 , 4.1 </t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Mysore-Sandal-Lavender-150gms-Luxury/dp/B092ZQDFX3/ref=sr_1_5?crid=3E8GRK3IKCRMX&amp;dib=eyJ2IjoiMSJ9.ZSj41siL7xTw0ci5d3IzjZinivlUrFyWI1iKAxwZAVp_7Fm9vf982pI8cSUzq8z5Kg8XW5O0OnMazsKjXVaP8KbYBWofUZx-mXHlQEWTBVdfgF3ufBmvyhBhpSHyO2kqmQ-CBy4M2Rdfv9nDw7J6VhV-p33GuUZPps62QWe6bL6pgdu6xAOYXctVPw-R5jRvQVeSuQhJc7efcPV_2CWK-mfoqypHcuruQ-Lz5aa4xDPuZdWWaU7gl6etlt46l5OErAJ_wANpfyRKrpob6KfwNaksuiuKsLc-C-nEyvkYSPw.JhktiTqCcyf2gMUH439yGlQxj_lUt308CzjhvtjUXDM&amp;dib_tag=se&amp;keywords=mysore%2Bsandal%2Blavender%2Bsoap&amp;qid=1772555347&amp;sprefix=mysore%2Bsandal%2Blavend%2Caps%2C372&amp;sr=8-5&amp;th=1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Sharans Natural: 25 , 5.0 </t>
+  </si>
+  <si>
+    <t>https://www.flipkart.com/sharans-natural-lavender-soap-herbal-bathing-soap-essential-oils/p/itm2acc45adcd608?pid=SOPH7DMR5M5VPCA5&amp;marketplace=FLIPKART&amp;lid=LSTSOPH7DMR5M5VPCA5AKGZIG&amp;q=sharans+natural+lavender&amp;fm=Search&amp;pageUID=1772555714256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Fiama Lavender: 700+ , 4.5 </t>
+  </si>
+  <si>
+    <t>https://blinkit.com/prn/fiama-moisturizing-soap-bars-japanese-hokkaido-milk-acai-berry/prid/598189</t>
+  </si>
+  <si>
+    <t>3. JioMart (AE Naturals): (New Entrant)</t>
+  </si>
+  <si>
+    <t>Bold Man D Tan Soap</t>
+  </si>
+  <si>
+    <t>Multani Mitti &amp; Turmeric</t>
+  </si>
+  <si>
+    <t>1. Ghar Soaps Magic: 145 , 4.7  (12k+ )</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Sandalwood-Saffron-Paraben-Handmade-Brightening/dp/B0CXXQL33D/ref=sr_1_1_sspa?crid=27O0P0YXZ963B&amp;dib=eyJ2IjoiMSJ9.le6p7LePXnRTqT5OSZziQ2CrgW-8l42gEeqkUsDDgilXkxtyeoWeSBq4B0_CVgRQ5nb1g1C-WMFDiaBAGVXJMV5uGjqjR2CNvRh_eAxUqpmyG6kIRRVtXeskOhMZzJwDEPkaXYCBuk1xCPJ7HYkaTwaiYv6mym58xeGOHIvNPsfKBTS1c0SpNgW1kUNVc6z1VP3EmnQ4YeoB5ka5vZzX0acboSOMBl0If353kwQr74RbFUffB_AxZ0Asjk5LCH5EG8-2QbjnvjXD2o3angDcu4yvCHLrLdk3lsJtfwa9DV4.r_2VKfdeAsEytHGsTAvp6IvWugAf9Vf-gfyx5KFWgCM&amp;dib_tag=se&amp;keywords=ghar%2Bmagic%2Bsoap%2Bmultani%2Bmitti&amp;qid=1772556078&amp;sprefix=ghar%2Bsoaps%2Bmagic%2Bmultani%2Caps%2C369&amp;sr=8-1-spons&amp;aref=uXNAM2pQv0&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Ghar Soaps Magic: 300+ , 4.0 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Bombay Shaving Co: 350+ , 4.3 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Meesho (Shobha's): 5 , 4.0 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Sanfe Instant: 412 , 4.9 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Nature Leaf D-Tan: 80% visibility, 4.0 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Mamaearth Ubtan: 600+ , 4.5 </t>
+  </si>
+  <si>
+    <t>https://blinkit.com/prn/mamaearth-ubtan-moisturizing-lotion-soap/prid/544863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Meesho (Winry): 10+ , 3.4 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Kozicare Gluta: 2k+ , 4.2 </t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Kozicare-Remover-Glowing-Moisturizing-Brightening/dp/B0C74FVD9Q/ref=sr_1_1_sspa?crid=2NZ24BJS6NKMC&amp;dib=eyJ2IjoiMSJ9.JTm-2TBl7rutPxZtv37BamnuPJcLoKhpWrc96lbfykCbgon60d23HNXqp0WnPZkqGlTHB6Xt70iLkL_ARRT6BIB44YqxeQp_s_8PnpjD9iWA1OzW2q8hL8dLzi71sJeVZ5SD4wsIMLE3_iGp-i1PaGWH0LBrXFdr7mqNViAHszMEITRdOmfdmlG4hTECyEMSQVmFmPn7jme7cz8QcDGdUDFKwvOE9e2SREqQ5k9c8shC-vq9PT2gr71_lE2AdcHM0BozCDSUkdY43ozXJd9A74Yu20dNm5h9cskaj3qWH_0.d45nSCArK4U2_sI2KF-bqYu-No5tVVg3gcCZpw1qW3U&amp;dib_tag=se&amp;keywords=kozicare+gluta+multani+mitti+and+turmeric&amp;qid=1772556201&amp;sprefix=kozicare+gluta+multani+mitti+and+turme%2Caps%2C344&amp;sr=8-1-spons&amp;aref=O3icccosYY&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;psc=1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. GHAHV Magic: 50+ , 2.7 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Ghar Soaps: 120+ , 4.6 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. JioMart (Lacto Calamine): 450 , 4.4 </t>
+  </si>
+  <si>
+    <t>Tru Basic Neem Charcoal</t>
+  </si>
+  <si>
+    <t>Activated Bamboo Charcoal</t>
+  </si>
+  <si>
+    <t>1. Bombay Shaving Co: 1.7k , 4.1  (20k+ )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Herbatol Plus: 415 , 4.2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Bombay Shaving Co: 1k+ , 4.2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Meesho (V Care): 26 , 4.2 </t>
+  </si>
+  <si>
+    <t>2. The Man Company: 4k+ , 4.8  (15k+ )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. YUAR Essential: 8 , 4.5 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. The Man Company: 900 , 4.7 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Meesho (Zeroic): 29 , 3.9 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Mamaearth Charcoal: 3k+ , 4.4 </t>
+  </si>
+  <si>
+    <t>3. Bombay Shaving Co: (Top search result)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Pears Oil Clear: 1.5k , 4.5 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. JioMart (Lacto Calamine): 800 , 4.1 </t>
+  </si>
+  <si>
+    <t>Tru Basic Chandan Kesar</t>
+  </si>
+  <si>
+    <t>Saffron (Kesar) &amp; Sandalwood</t>
+  </si>
+  <si>
+    <t>1. Mysore Sandal Pure: 25k+ , 4.6  (100k+ )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Mysore Sandal Gold: 15k+ , 4.5 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Mysore Sandal: 3.5k , 4.6 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Meesho (Pureindia): 25 , 3.9 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Moha Kesar Chandan: 101 , 4.5 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Kozicare Sandal: 349 , 4.0 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Santoor Sandal: 8k+ , 4.5 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Meesho (ZOOMZ): 43 , 4.2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Ubtan India: 50+ , 4.2 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. GLIVORA Chandan: 20+ , 4.8 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Medimix Sandal: 2.2k , 4.4 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. JioMart (Moha): 15+ , 4.4 </t>
+  </si>
+  <si>
+    <t>Bold Man Charcoal Soap</t>
+  </si>
+  <si>
+    <t>1. The Man Company: 4k+ , 4.8  (Premium Male Search)</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Man-Company-Charcoal-Nourishes-Toxin-free/dp/B09WDYDM2C/ref=sr_1_5?dib=eyJ2IjoiMSJ9.TkwkWTWWMX3g_YbKWtbQtycUFIzIiS1RBtVmILPn5--e_Otxq626XmbvB0GJMFJ6W4ZUQoYU0h9g_fAybOcxfMP5UPjB0tLfDHi5Oxf6HjbRRLGa1f_OgQFXajnvUlri7cHmOAjzQTiQ4ACGwA1BdoUyKPh9nGfpK5IjwQ3jWZa43NGNtAxxXI5MDUbG8_9M0RjeR_jg9eUUP6wEAhWHMyEiqmNDm_PZky3C0JxDQI0USfvpY5_JG0KxnDTFdyhZp2F2iIGEj6qIbWTz3aGMV7adgp_NBxCZeMM-iHqdXLY.5yTBrRZITq2g5Png0NBeZWyAwl8ZCP0i1uIxueZnmKE&amp;dib_tag=se&amp;keywords=the+man+company+male+soap&amp;qid=1772345330&amp;sr=8-5</t>
+  </si>
+  <si>
+    <t>1. 7Days Charcoal: 64% Discount search leader</t>
+  </si>
+  <si>
+    <t>https://www.flipkart.com/7-days-charcoal-bath-soap-handmade-deep-cleansing-daily-bathing-bar-men/p/itm329b7815e406c?pid=SOPG4UJTHDQDJFZZ&amp;lid=LSTSOPG4UJTHDQDJFZZHNB5LM&amp;marketplace=FLIPKART&amp;q=7+days+charcoal+soap&amp;store=g9b%2F5nz%2Fb1b%2Fyug&amp;srno=s_1_3&amp;otracker=search&amp;otracker1=search&amp;fm=Search&amp;iid=07a59be6-6fb9-43b7-bb18-15c67785bcc1.SOPG4UJTHDQDJFZZ.SEARCH&amp;ppt=sp&amp;ppn=sp&amp;ssid=b8yj5h2wsw0000001772345945165&amp;qH=235ac1e5b50c344b&amp;ov_redirect=true&amp;ov_redirect=true</t>
+  </si>
+  <si>
+    <t>1. Nivea Men Clean: (High velocity)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Meesho (Activated): 347 , 3.7 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Bombay Shaving Co: 1.7k , 4.1 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Mannlich Kojic: 299 , 4.2 </t>
+  </si>
+  <si>
+    <t>https://www.flipkart.com/mannlich-2-kojic-skin-brightening-soap-men-reduces-dark-spots-tan-pigmentation/p/itm2b211969b05f9?pid=SOPH7PS7APWMWJ2P&amp;lid=LSTSOPH7PS7APWMWJ2PKLYMWY&amp;marketplace=FLIPKART&amp;q=mannlick+kojic+soap&amp;store=g9b%2F5nz%2Fb1b%2Fyug&amp;srno=s_1_2&amp;otracker=search&amp;otracker1=search&amp;fm=Search&amp;iid=en_MjZhVba8AzjZpcPnt9lnw93Ij3zLniKGlyJhYs9he_5e6XBGWtBS9HrCodnsL5nt8_IfwFUMn6jTobJhiNRIo9mEaX_1OVaDgohoY5ZV-y8%3D&amp;ppt=sp&amp;ppn=sp&amp;ssid=cd1t3jlskg0000001772345975087&amp;qH=c6edf37828b19050&amp;ov_redirect=true&amp;ov_redirect=true</t>
+  </si>
+  <si>
+    <t>2. Beardo Charcoal: (Top of list)</t>
+  </si>
+  <si>
+    <t>2. JioMart (Denver): 3.0 boxes sold monthly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Park Avenue Luxury: 2.3k , 4.3 </t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Park-Avenue-Pure-Luxury-500gm/dp/B0B6ZXHMX7/ref=sr_1_6?crid=2T2A80ORS5HF8&amp;dib=eyJ2IjoiMSJ9.zEbMnqcEijPDY-lUhSdnKANx1JyrYQoEcpGSamHfU-M6LwbFI1VjfevWurGO2wVVYJKNNZ-a6pr2Z9fknNvfjIZavlJtGD0OFtHdf0MhS__8JnuKHhh6aZ-P42i92gEXM50HboyBr3RpM23QD5KpYmmRsBeBY2h_kwSh8ma1FCarJqeLyOC0iB1HgLMdxW0MwzgRvmr7xFqSCWjDEEOoEbibRNcvyOjvchEgAli6oISQlktSm4IpU8MvubyeIZougd68gQio-mULpuyaHRfcP8MxlZ18OHeyUNZWGzPVNT0.mNxdp-O6KSkz4wrLUQLbS-qDxqj6i3BVM-6kBed33zE&amp;dib_tag=se&amp;keywords=park+avenue+soap&amp;qid=1772345490&amp;sprefix=park+avenue+soap%2Caps%2C442&amp;sr=8-6</t>
+  </si>
+  <si>
+    <t>3. ARAMUSK Men: 38% Discount top result</t>
+  </si>
+  <si>
+    <t>https://www.flipkart.com/aramusk-wipro-soap-men-classic-musk-fragrance/p/itmc329457984697?pid=SOPGF2QFVSZGXTWJ&amp;lid=LSTSOPGF2QFVSZGXTWJTKKDAQ&amp;marketplace=FLIPKART&amp;q=aramusk+men+soap&amp;store=g9b%2F5nz%2Fb1b%2Fyug&amp;srno=s_1_2&amp;otracker=search&amp;otracker1=search&amp;fm=Search&amp;iid=258b0fad-dfbe-48bc-8678-3a2e4350a223.SOPGF2QFVSZGXTWJ.SEARCH&amp;ppt=sp&amp;ppn=sp&amp;ssid=0lxp3d09m80000001772346050878&amp;qH=b34d932bb26edce4&amp;ov_redirect=true&amp;ov_redirect=true</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Bombay Shaving Co: 1.2k , 4.2 </t>
+  </si>
+  <si>
+    <t>3. Moglix (Oil Blend): (Price Rival)</t>
+  </si>
+  <si>
+    <t>Tru Basic Moisturizing</t>
+  </si>
+  <si>
+    <t>Vitamin E &amp; Aloe Vera</t>
+  </si>
+  <si>
+    <t>1. Dove Cream Beauty Bar: 85k+ , 4.7  (150k+ )</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Dove-Beauty-Bathing-Moisturizing-Smoother/dp/B008KH5FBE/ref=sr_1_5?crid=342M3CG71F9VY&amp;dib=eyJ2IjoiMSJ9.E9UI4CGCO20-fTfmKoBe4etDyO7sr_YD7FhZtCuNUPMRC6qq2uiYPkYcTby1lih2VJBWVEOPR6XXiOOFJ0To35t_QZ68Ji2WpJMMf9fM5lq2ANFxpZIQrYrJgR8pf8g0eHDpwi1rsCSTIbTZwztT1W9jnjo6wzZktMbN6r_lLY5rSq1H3ZBIdtNKZL6t7xwvk34oescTin9IbxUJasA9jWJSBDGdr_zUfL9aOVvmpE3g62YRtZB9Auy4-ZYzBOZQYQhcKTwXJdXytkUlgu6xlU2Sou_kIjOoBUExheRieFA.I-SQq6KEltISMUB9snsDEn0h05c8oFho9Q0P3H4CGA8&amp;dib_tag=se&amp;keywords=dove+cream+beauty+bar&amp;qid=1772518029&amp;sprefix=dove+cream+%2Caps%2C432&amp;sr=8-5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Dettol Skincare: 1.2k , 4.3 </t>
+  </si>
+  <si>
+    <t>https://www.flipkart.com/dettol-skincare-moisturizing-bathing-soap-argan-oil-softer-skin/p/itm1d76fe0b7b56b?pid=SOPH4M2BQCDNTTPK&amp;lid=LSTSOPH4M2BQCDNTTPKXVQGRF&amp;marketplace=FLIPKART&amp;q=dettol+soap&amp;store=g9b%2F5nz%2Fb1b%2Fyug&amp;srno=s_1_10&amp;otracker=AS_QueryStore_OrganicAutoSuggest_2_7_na_na_na&amp;otracker1=AS_QueryStore_OrganicAutoSuggest_2_7_na_na_na&amp;fm=search-autosuggest&amp;iid=b21e9d6e-054a-4f7e-bd2b-a35c5c57bf89.SOPH4M2BQCDNTTPK.SEARCH&amp;ppt=sp&amp;ppn=sp&amp;ssid=1plwxekgdc0000001772518169768&amp;qH=550a310d5e7960a1&amp;ov_redirect=true&amp;ov_redirect=true</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Dove Cream Bar: 5k+ , 4.7 </t>
+  </si>
+  <si>
+    <t>https://blinkit.com/prn/dove-cream-beauty-bathing-soap-3-x-125-g/prid/445815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Meesho (Ovium): 20+ , 4.4 </t>
+  </si>
+  <si>
+    <t>https://www.meesho.com/ovium-pack-of-4-400g-neem-handmade-natural-soaps-for-bath-all-skin-type-skin-brightening-soap-for-men-women/p/bu0pac</t>
+  </si>
+  <si>
+    <t>2. Pears Pure &amp; Gentle: 45k+ , 4.5  (80k+ )</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Pears-Pure-Gentle-Bathing-Pack/dp/B07BNS25DB/ref=sr_1_5_in_f3_0o_fs_mod_primary_alm?crid=3FH3PR8VY4K2A&amp;dib=eyJ2IjoiMSJ9.PFSn9cSFFb3UTkbeMtM74-y_8K20PgM7BJiqMY16Dvlb0zArsI7EfYrDQvxK6E3tj2FlLF24T7znZIw1mZGLisEvnpvXIKbdpX1U4Ev3hSEzWpejjQMv-Dd1s0C7Y8eJR_LzFWhTgu2Q8x6fsFspIz9FW7oMJH--2h_XiDDZLYMWpJCcWjkOcgOS3NZYlyCyKtYoStOsnw2vdMuRDMvDSLAKgh4XEMZmD6SAr09ZSZGn2m_xx2G4INuEgMgEzz8ReJO0SpFbcG5mbVoyPAZMzBaKEIHcHsp9ycQZPFRAWaE.bSwwRkLZGvkVTZ4Bmky1xXiuOMzpDUuxYGgfdZDryH4&amp;dib_tag=se&amp;keywords=pears+pure+and+gentle+soap+pack&amp;qid=1772518097&amp;sbo=m6DjfpMzMLDmL8pSMKX8hw%3D%3D&amp;sprefix=pears+pure+and%2Caps%2C393&amp;sr=8-5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Savlon Aloe: 300+ , 4.4 </t>
+  </si>
+  <si>
+    <t>https://www.flipkart.com/savlon-glycerin-soap-bar-protection-natural-origin-glycerin-120g-combo-pack/p/itm2b72172993829?pid=SOPH2KMSMSTCZ363&amp;lid=LSTSOPH2KMSMSTCZ363QWUEQR&amp;marketplace=FLIPKART&amp;q=savlon+aloe+soap&amp;store=g9b%2F5nz%2Fb1b%2Fyug&amp;spotlightTagId=default_BestsellerId_g9b%2F5nz%2Fb1b%2Fyug&amp;srno=s_1_1&amp;otracker=search&amp;otracker1=search&amp;fm=Search&amp;iid=3276c7fb-9521-41a2-bc4d-8bd85416bfd0.SOPH2KMSMSTCZ363.SEARCH&amp;ppt=sp&amp;ppn=sp&amp;ssid=7aevh18t7k0000001772518231655&amp;qH=b4c5203df34f8063&amp;ov_redirect=true&amp;ov_redirect=true</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Pears Pure: 3k+ , 4.5 </t>
+  </si>
+  <si>
+    <t>https://blinkit.com/prn/pears-pure-gentle-soap/prid/19481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Meesho (Premium): 50+ , 3.9 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Wow Skin Science: 203 , 4.2 </t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/WOW-Skin-Science-Moisturising-Moisturisation/dp/B0DZNMTGVF/ref=sr_1_5_in_f3_0o_fs_mod_primary_alm?crid=1BGLB7LK0OUIX&amp;dib=eyJ2IjoiMSJ9.AVktFSvi6Pl7z4bHQYO-OWBJk0-SVoEtF6Sh-NVELCr8GHftsoyT1wx6dkV4CZZJgMRnIHev7gzETOo2s1ZrUSnZromCai-zl0avbNk3ktgTsPxaujGrd3ZmKQhjqEpdSoEgVrw9um54x80OYy8--5eMDBNbn9vs12IO_0JMnJn6goCso2AD0TN5I4Zr6IBHjvVpjxUWZ47rs1abv41KJIryfC_7LR2Y0U3uGIEYsk4ebS9ilGWXMruW7vrNGyfiNgPBG2fpol7hJBu836rPEWW8qw_3f40sy7LQWxrFJqo._91SbqGk0Km0IV_VVLaPhtW00wWCpkn_a9i1f3pbOcI&amp;dib_tag=se&amp;keywords=wow+skin+science+soap&amp;qid=1772518133&amp;sbo=m6DjfpMzMLDmL8pSMKX8hw%3D%3D&amp;sprefix=wow+skin+science+oap+%2Caps%2C405&amp;sr=8-5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Aaryanveda Aloe: 234 , 4.2 </t>
+  </si>
+  <si>
+    <t>https://www.flipkart.com/aaryanveda-aloe-vera-bathing-bar-soothing-moisturizing-skin-alovera-neem-body-soap/p/itm41d7b4c7ca778?pid=SOPGW3FU45FSGMWW&amp;lid=LSTSOPGW3FU45FSGMWWHCPAYY&amp;marketplace=FLIPKART&amp;q=aaryanveda+aloe+soap&amp;store=g9b%2F5nz%2Fb1b%2Fyug&amp;srno=s_1_4&amp;otracker=search&amp;otracker1=search&amp;fm=Search&amp;iid=e85263d2-e266-4a67-be8f-6a5740e6c395.SOPGW3FU45FSGMWW.SEARCH&amp;ppt=sp&amp;ppn=sp&amp;ssid=66x9rk5ag00000001772518253684&amp;qH=67718f9e75cf60d6&amp;ov_redirect=true&amp;ov_redirect=true</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Nivea Creme Soft: 1.2k , 4.4 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. JioMart (Pears): 1.8k , 4.5 </t>
+  </si>
+  <si>
+    <t>https://www.jiomart.com/p/groceries/pears-pure-gentle-soap-125-g-buy-4-get-1-free/491085658</t>
+  </si>
+  <si>
+    <t>Tru Basic Glowing</t>
+  </si>
+  <si>
+    <t>Alpha Arbutin &amp; Kojic Acid</t>
+  </si>
+  <si>
+    <t>1. Kozicare Skin Light: 26k+ , 4.0  (20k+ )</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/sspa/click?ie=UTF8&amp;spc=MToyNDI4MDI2MjIxNTkyMjM4OjE3NzI1MTg4MTA6c3BfYXRmOjMwMDEyMDMxMjcxNDgzMjo6MDo6&amp;url=%2FKozicare-Brightening-Sulphate-Artificial-Fragrance%2Fdp%2FB0C74DCWDZ%2Fref%3Dsr_1_1_sspa%3Fcrid%3D2ILRNDUNHCLCF%26dib%3DeyJ2IjoiMSJ9.acuKbHuqipfJDwy9tNRUfBUMRjS4jy0LW6fSEvIUdr7EyGlFBF2UJjXbCBtvoUuXw6LPXu_wPVBx2kN1f2_l9kIOLuKbC-PVfuidwyVehTyYJebVxjZ_DIuAruHjuDEfGdNBKTowddSW_5xl23ImDFnbrDsBpkI03XNRT4K8Y8Kl3t-rf-BBijzdZ19HW98YU1kLv_XLqjIN1HaqdHUqSMv1YMYGdVwe2FuEaecOsx3ebt2JZb_tN3jD5-5Y78ij0vPRgColBxSQpkU9K7yAkZ3IdCOarf2EqLhSTJ19OwY.6JTzWZzoMhsYhKK_om03rLiOh-eNVHOqdxsWLrt6LTE%26dib_tag%3Dse%26keywords%3Dkozicare%2Bskin%2Blight%2Bsoap%26qid%3D1772518810%26sprefix%3Dkozicare%2Bskin%2Blig%2Bsoap%252Caps%252C393%26sr%3D8-1-spons%26aref%3D7198TPBtPu%26sp_csd%3Dd2lkZ2V0TmFtZT1zcF9hdGY%26psc%3D1&amp;aref=7198TPBtPu&amp;sp_cr=ZAZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Kozicare Saffron: 475+ , 4.3 </t>
+  </si>
+  <si>
+    <t>https://www.flipkart.com/kozicare-saffron-soap-skin-brightening-dark-spot-remover-75gm-pack-6/p/itm6535c9cefa3b6?pid=SOPGQZA6WBEA4FSU&amp;lid=LSTSOPGQZA6WBEA4FSUIYTEEM&amp;marketplace=FLIPKART&amp;q=kozicare+saffron+soap&amp;store=g9b%2F5nz%2Fb1b%2Fyug&amp;srno=s_1_1&amp;otracker=search&amp;otracker1=search&amp;fm=Search&amp;iid=en_dOhZoceoLjxYzI6kbe_swx_TNxq07yySUeT5G5I3bZCw8W6Q7A3PBDSHWjuGBVmxncd6bitpgwznk2229Ukoek4IsYyWu-Pj9cxFjFAoaLk%3D&amp;ppt=sp&amp;ppn=sp&amp;ssid=ehz555kwxs0000001772518893188&amp;qH=d3ff065778c555d4&amp;ov_redirect=true&amp;ov_redirect=true</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Sanfe Glow Bar: 150+ , 3.9 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Meesho (Scarled): 13 , 3.5 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Dermatouch 1%: 26k+ , 4.0 </t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/sspa/click?ie=UTF8&amp;spc=MTo4NjYyMjU0MjQ4MDMzODYxOjE3NzI1MTg4MzM6c3BfYXRmOjMwMDE1NzMyMDExNjQzMjo6MDo6&amp;url=%2FDERMATOUCH-Glutathione-Pigmentation-damage-Suitable%2Fdp%2FB0CZXY9LNZ%2Fref%3Dsr_1_1_sspa%3Fcrid%3D32BXKAA1T1RLK%26dib%3DeyJ2IjoiMSJ9.88yMbp0inw99Wv4-cTJFRMC5A_OAPUct-XBklBEIxQAb-t5cu7g3ZA_zUBw3TTcScK2-OluV1wnidh2cB5tw3htVPPQdL_fzU01r9VHD_0YvLTERGbvEfXm7sbawHVsxQbix2gr3FKx97f1NRNYTKxkJUR9MpqYVRwNi7J6KfNbkLJQWM8awjJ9OZ1MDQHcBnkPQlBDdqkO763CqhOM2dW57E_YIPv3LS_7ToShr_MfJ0x0OeqHoCwjX3dhMQMNtZFkLgvTYGQKMj3B4fuq78Hpzmoek6IItmwEmRKK4P94.AEPXaYeuVQwxrPq991ZwQARgVLnjUM6h56309Cj09x0%26dib_tag%3Dse%26keywords%3Ddermatouch%2B1%2Bsoap%26qid%3D1772518833%26sprefix%3Ddermatouch%2B1%2Bsoap%252Caps%252C393%26sr%3D8-1-spons%26aref%3D27iVAlLKpl%26sp_csd%3Dd2lkZ2V0TmFtZT1zcF9hdGY%26psc%3D1&amp;aref=27iVAlLKpl&amp;sp_cr=ZAZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Dermatouch Kojic: 26k , 4.0 </t>
+  </si>
+  <si>
+    <t>https://www.flipkart.com/dermatouch-kojic-acid-1-soap-glutathione-pigmentation-sun-damage/p/itmd9df2b786e8d5?pid=SOPGZSYXHZ5PVGQW&amp;lid=LSTSOPGZSYXHZ5PVGQWIQ1PUM&amp;marketplace=FLIPKART&amp;q=dermatouch+kojic+soap&amp;store=g9b%2F5nz%2Fb1b%2Fyug&amp;spotlightTagId=default_BestsellerId_g9b%2F5nz%2Fb1b%2Fyug&amp;srno=s_1_1&amp;otracker=search&amp;otracker1=search&amp;fm=Search&amp;iid=e076a11f-6b09-444e-9a10-cdc14a2ffdd6.SOPGZSYXHZ5PVGQW.SEARCH&amp;ppt=sp&amp;ppn=sp&amp;ssid=y44qwqsobk0000001772518914435&amp;qH=18d84118f254f261&amp;ov_redirect=true&amp;ov_redirect=true</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Kozicare Kojic: 200+ , 4.0 </t>
+  </si>
+  <si>
+    <t>https://blinkit.com/prn/kozicare-skin-lightening-soap/prid/555063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Meesho (Glamveda): 56 , 3.7 </t>
+  </si>
+  <si>
+    <t>https://www.meesho.com/glamveda-2-kojic-acid-soap-with-niacinamide-for-pigmentation-uneven-skin-tone-reduces-dark-spots-sun-tan-skin-brightening-soap-for-men-women-kojic-acid-fairness-soap-pack-of-2-150gm/p/751dhk</t>
+  </si>
+  <si>
+    <t>Godrej Kesar soap (JioMart)</t>
+  </si>
+  <si>
+    <t>https://www.jiomart.com/p/groceries/godrej-no-1-kesar-milk-cream-150-g-buy-3-get-1-free/590127131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Co Luxury Gluta: 191 , 4.0 </t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/CO-Glutathione-Brightening-Vitamin-Pigmentation/dp/B0CTXF4LNS/ref=sr_1_5?crid=29MDNM4X8SXZ0&amp;dib=eyJ2IjoiMSJ9.eME_h_05BGHf8m6EAfVzuOjzF7edW33dXiMkddBO3rgw0XNoQ8wGBkKe1tSHmvSNNeI9eQeWjnX6WAcu9wzn8-6za8G6RA4x1FnXB1h1KqkNHB-zgc73pgBpUOUvQjn3-2nBbGbe7TqJRj3KEG5jI3P8Kco0JIzUWFRW6YNup5-T-jDttvIEy-0YML4zCX_pTG61_NdAhIm8EHFl5_lLtla8B9PmDkVvjJIdHEuvVCrag9hBifJOWQOhUr0RDi8hOMibhNvDZcUEdrtV00AEQZMTQ_6GG7hTSb_PfyV1J_o.rr9gI6wvPac1J6YgGe_ors65wK1vzkONrAZqaahw7rw&amp;dib_tag=se&amp;keywords=co+luxury+gluta+soap&amp;qid=1772518852&amp;sprefix=co+luxury+glut+soap%2Caps%2C386&amp;sr=8-5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Tru Basic Glowing: 297 , 4.0 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Mamaearth Vit C: 500+ , 4.4 </t>
+  </si>
+  <si>
+    <t>https://blinkit.com/prn/mamaearth-vitamin-c-moisturizing-lotion-soap/prid/544865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. JioMart (Sanfe Kesar): 181 , 4.7 </t>
+  </si>
+  <si>
+    <t>Tru Basic Honey Lemon</t>
+  </si>
+  <si>
+    <t>Honey &amp; Lemon Oil</t>
+  </si>
+  <si>
+    <t>1. Cinthol Lime: 65k+ , 4.5  (150k+ )</t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Cinthol-Lime-Soap-100g-Pack/dp/B01A8TM9K6/ref=sr_1_5_in_f3_0o_fs_mod_primary_alm?crid=3OH6QVRBAB8UP&amp;dib=eyJ2IjoiMSJ9.hilXOU7aVqjHCKy1RftmmYjMpM3jo_Wx92vtBxU5dhl6C8-TiX7g511KUJNEaKJYXFrv1CzFR44LHGr45xwX8JnkBK7NAb3Vln_Ya4-o_PoNvvRxBccDMAoiTvdhvmwN4LI7qFVSy5BqS2uvzHnL44vPoxAw0bOo8tzwoCMcHAoMOC4fE8ffD8ULRwKcJqSbWLsvrb6sdOXtGgQY-nsvTb_rVKx_FUKLoDJDVhiq_YRg4fnRAqzde4axMfCyrVcEuu5XLGZyv80jxDtVFQYGAODbfXL1dow8amg2oVSSues.Qbp60xQLLrwdouv6GzviGFXW5Em5rF-c8gLtZcJ9Zic&amp;dib_tag=se&amp;keywords=cinthol+lime+luxury+gluta+soap&amp;qid=1772519165&amp;sbo=m6DjfpMzMLDmL8pSMKX8hw%3D%3D&amp;sprefix=cinthol+li+luxury+gluta+soap%2Caps%2C402&amp;sr=8-5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Gharsoaps Kojic White Honey: 36 , 4.0 </t>
+  </si>
+  <si>
+    <t>https://www.flipkart.com/gharsoaps-kojic-acid-2-soap-niacinamide-reduce-pigmentation-all-skin-types/p/itm685d710451843?pid=SOPHYRFEGKMFVFS5&amp;lid=LSTSOPHYRFEGKMFVFS54OZWKM&amp;marketplace=FLIPKART&amp;q=kojic+white+honey+soap&amp;store=g9b%2F5nz%2Fb1b%2Fyug&amp;srno=s_1_9&amp;otracker=search&amp;otracker1=search&amp;fm=Search&amp;iid=30e2806b-b6eb-4794-9661-62d7d4c85a98.SOPHYRFEGKMFVFS5.SEARCH&amp;ppt=sp&amp;ppn=sp&amp;ssid=fjeyb5u24g0000001772519260425&amp;qH=c1766f9de2bf20b2&amp;ov_redirect=true&amp;ov_redirect=true</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Cinthol Lime: 4.5k , 4.5 </t>
+  </si>
+  <si>
+    <t>https://blinkit.com/prn/cinthol-lime-bath-soap-5-x-100-g-buy-4-get-1-free/prid/23803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Meesho (Best One Store): 1 rev, 3.0 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Godrej No. 1 Lime: 35k+ , 4.4 </t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/Godrej-No-1-Lime-Aloe-Vera/dp/B01DLU1PIG/ref=sr_1_5?crid=2SVL3LHEOEI0W&amp;dib=eyJ2IjoiMSJ9.KMcwWQAAf-gRB4bdwMVuZHvIqKlBax8622J7l6Kjhkp4O9VwxDQn2ZqlPIrHQId3hpOdv2taN5XEvgnYFPhNbeaHC6G_YcTYCOQyFtc6Rhf4AGlNUsd9Fw4k71huqoTE5mc8ASULurM1YWRE1ki0N0pzAftlQiLc_lQQL-3oXwHyxApiBiwwLLrPLFmZbj-DxZ_SJPnYBLNPKfgP2CKjJFzrdRaO3Eb0NQ7RuL0_f2bIFUxp0lxO7OCicbAqoXdW8a0QuqVP3Da8xUgxi2UA4lIHMIcDQpKTqlJUMeoJrbk.pf6ziP06Aeozw_8XBRwQNNk97IeGQJsIYbI51oCRO6w&amp;dib_tag=se&amp;keywords=godrej+lime+soap&amp;qid=1772519196&amp;sprefix=godrej+lime+soap%2Caps%2C403&amp;sr=8-5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. PINKROOT Honey: 10+ , 4.4 </t>
+  </si>
+  <si>
+    <t>https://www.flipkart.com/pinkroot-honey-lemon-soap-100gm-pack-3/p/itm5f1976584ef0b?pid=SOPGFCCZKHFTZQUH&amp;lid=LSTSOPGFCCZKHFTZQUHZ5EIGU&amp;marketplace=FLIPKART&amp;q=pinkroot+honey+soap&amp;store=g9b%2F5nz%2Fb1b%2Fyug&amp;srno=s_1_3&amp;otracker=search&amp;otracker1=search&amp;fm=Search&amp;iid=b701e6ef-8ca8-4ee3-adec-5e2060fc2af4.SOPGFCCZKHFTZQUH.SEARCH&amp;ppt=sp&amp;ppn=sp&amp;ssid=goi2vuad0w0000001772519333732&amp;qH=5a28db6558195f88&amp;ov_redirect=true&amp;ov_redirect=true</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Fiama Lemon: 2.8k , 4.5 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. Meesho (Khadi Natural): 150+ , 4.1 </t>
+  </si>
+  <si>
+    <t>https://www.meesho.com/premium-kahdi-lemon-grass-soap-125g-pack-of-2/p/1ib2qr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Khadi Honey/Lemon: 1.5k , 4.2 </t>
+  </si>
+  <si>
+    <t>https://www.amazon.in/sspa/click?ie=UTF8&amp;spc=MToyNTgzODU1OTU5NTQ1NzA4OjE3NzI1MTkyMjY6c3BfYXRmOjMwMDY0Mzg5ODMwNDAzMjo6MDo6&amp;url=%2FKhadi-Natural-Lemon-Soap-125g%2Fdp%2FB00ZTYLFQA%2Fref%3Dsr_1_2_sspa%3Fcrid%3D28SHYNS9WQ6CS%26dib%3DeyJ2IjoiMSJ9.ht8z40ulreheNy2gm2LdqpCF2wiVG-go9SK3cFBy8Fc-JeEpuoF9NXDj6S6bdxrfwClbxob4WyBnRAG_MbZtbq_mHSf417So0B1XQj6XYALoXqldjJv6FYjxQcuVN1gCJgC4VUTScsajxzwaqZlFJ_RnwLp_3zO7JuEZOmDEt7W3V-83MnZbnTSRhM5XLFyPA71e2wyZYXxg8VBBxNQ3XOx_oqZ0HOni5imfvHJsKUTUgCyhwPCeTE-TbUdrYbFG4CEcFxGF6Rhs_Tdu8jOW59t90E8LhctNeCNY9MuvY7k.rispD3QuKzksWvkwjhXrLwtDqj47y__AcYF3zRN1Bjw%26dib_tag%3Dse%26keywords%3Dkhadi%2Bhoney%2Blemon%2Bsoap%26qid%3D1772519226%26sprefix%3Dkhadi%2Bhoney%2Blemon%2Bsoap%252Caps%252C381%26sr%3D8-2-spons%26aref%3DLoA1Uvqqik%26sp_csd%3Dd2lkZ2V0TmFtZT1zcF9hdGY%26psc%3D1&amp;aref=LoA1Uvqqik&amp;sp_cr=ZAZ</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Queen Temple: 5+ , 4.0 </t>
+  </si>
+  <si>
+    <t>https://www.flipkart.com/queen-temple-handmade-lemongrass-soap/p/itm0aba199b55b7a?pid=SOPH4YPYHSHG6B8Q&amp;lid=LSTSOPH4YPYHSHG6B8QZUQYCA&amp;marketplace=FLIPKART&amp;q=queen+temple+soap&amp;store=g9b%2F5nz%2Fb1b%2Fyug&amp;srno=s_1_3&amp;otracker=search&amp;otracker1=search&amp;fm=Search&amp;iid=c99a9983-3aa5-4553-b663-e853513df5a7.SOPH4YPYHSHG6B8Q.SEARCH&amp;ppt=sp&amp;ppn=sp&amp;ssid=bcg0lhzu3k0000001772519355451&amp;qH=a7ab22aa908c3189&amp;ov_redirect=true&amp;ov_redirect=true</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. Godrej No. 1 Lime: 5.5k , 4.4 </t>
+  </si>
+  <si>
+    <t>https://blinkit.com/prn/godrej-no.1-lime-aloe-vera-soap-4-x-150-g-buy-3-get-1-free/prid/365997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. JioMart (Soapery): 2+ , 5.0 </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="6" formatCode="&quot;₹&quot;#,##0_);[Red]\(&quot;₹&quot;#,##0\)"/>
-  </numFmts>
-  <fonts count="5">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -394,21 +778,15 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0F1111"/>
-      <name val="Amazon Ember"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="Calibri"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
       <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF0F1111"/>
+      <color rgb="FF1F1F1F"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -421,7 +799,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -429,12 +807,64 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -442,19 +872,68 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="6" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -772,12 +1251,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4A120A5-37CF-439A-80A6-887C4C7849B6}">
   <dimension ref="A1:V18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="16384" width="8.83203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="32">
+    <row r="1" spans="1:22" ht="32" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -842,7 +1321,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="2" spans="1:22" ht="320">
+    <row r="2" spans="1:22" ht="304" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>21</v>
       </c>
@@ -908,7 +1387,7 @@
       </c>
       <c r="V2" s="2"/>
     </row>
-    <row r="3" spans="1:22" ht="335">
+    <row r="3" spans="1:22" ht="320" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>21</v>
       </c>
@@ -974,7 +1453,7 @@
       </c>
       <c r="V3" s="2"/>
     </row>
-    <row r="4" spans="1:22" ht="409.6">
+    <row r="4" spans="1:22" ht="409.6" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>21</v>
       </c>
@@ -1040,7 +1519,7 @@
       </c>
       <c r="V4" s="2"/>
     </row>
-    <row r="5" spans="1:22" ht="176">
+    <row r="5" spans="1:22" ht="176" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>21</v>
       </c>
@@ -1106,7 +1585,7 @@
       </c>
       <c r="V5" s="2"/>
     </row>
-    <row r="6" spans="1:22" ht="128">
+    <row r="6" spans="1:22" ht="128" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>21</v>
       </c>
@@ -1172,7 +1651,7 @@
       </c>
       <c r="V6" s="2"/>
     </row>
-    <row r="7" spans="1:22">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D7" s="2"/>
       <c r="E7" s="2"/>
       <c r="F7" s="2"/>
@@ -1193,7 +1672,7 @@
       <c r="U7" s="2"/>
       <c r="V7" s="2"/>
     </row>
-    <row r="8" spans="1:22" ht="240">
+    <row r="8" spans="1:22" ht="240" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
         <v>21</v>
       </c>
@@ -1259,7 +1738,7 @@
       </c>
       <c r="V8" s="2"/>
     </row>
-    <row r="9" spans="1:22" ht="335">
+    <row r="9" spans="1:22" ht="304" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
         <v>21</v>
       </c>
@@ -1325,7 +1804,7 @@
       </c>
       <c r="V9" s="2"/>
     </row>
-    <row r="10" spans="1:22">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
@@ -1346,7 +1825,7 @@
       <c r="U10" s="2"/>
       <c r="V10" s="2"/>
     </row>
-    <row r="11" spans="1:22" ht="48">
+    <row r="11" spans="1:22" ht="48" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
         <v>43</v>
       </c>
@@ -1414,7 +1893,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:22" ht="288">
+    <row r="12" spans="1:22" ht="288" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
         <v>43</v>
       </c>
@@ -1480,7 +1959,7 @@
       </c>
       <c r="V12" s="2"/>
     </row>
-    <row r="13" spans="1:22" ht="144">
+    <row r="13" spans="1:22" ht="144" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
         <v>43</v>
       </c>
@@ -1546,7 +2025,7 @@
       </c>
       <c r="V13" s="2"/>
     </row>
-    <row r="14" spans="1:22" ht="144">
+    <row r="14" spans="1:22" ht="144" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
         <v>43</v>
       </c>
@@ -1612,7 +2091,7 @@
       </c>
       <c r="V14" s="2"/>
     </row>
-    <row r="15" spans="1:22" ht="144">
+    <row r="15" spans="1:22" ht="144" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
         <v>43</v>
       </c>
@@ -1678,7 +2157,7 @@
       </c>
       <c r="V15" s="2"/>
     </row>
-    <row r="16" spans="1:22" ht="192">
+    <row r="16" spans="1:22" ht="192" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
         <v>43</v>
       </c>
@@ -1744,7 +2223,7 @@
       </c>
       <c r="V16" s="2"/>
     </row>
-    <row r="17" spans="1:22" ht="48">
+    <row r="17" spans="1:22" ht="48" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
         <v>43</v>
       </c>
@@ -1812,7 +2291,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:22" ht="64">
+    <row r="18" spans="1:22" ht="64" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
         <v>43</v>
       </c>
@@ -1891,473 +2370,967 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBD3C3C7-C137-8C42-B950-EC8F59499332}">
-  <dimension ref="A1:J31"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <dimension ref="A1:J46"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" style="10"/>
-    <col min="2" max="2" width="25" style="10" customWidth="1"/>
-    <col min="3" max="3" width="10.83203125" style="10"/>
-    <col min="4" max="4" width="17.83203125" style="10" customWidth="1"/>
+    <col min="1" max="1" width="10.83203125" style="4"/>
+    <col min="2" max="2" width="25" style="4" customWidth="1"/>
+    <col min="3" max="3" width="10.83203125" style="4"/>
+    <col min="4" max="4" width="17.83203125" style="4" customWidth="1"/>
     <col min="5" max="5" width="38.33203125" customWidth="1"/>
-    <col min="6" max="6" width="14.33203125" customWidth="1"/>
+    <col min="6" max="6" width="44.5" customWidth="1"/>
+    <col min="9" max="9" width="38.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" s="8" customFormat="1">
-      <c r="A1" s="10" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="10" t="s">
+    <row r="1" spans="1:10" s="3" customFormat="1" ht="61" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C1" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="10" t="s">
+      <c r="C1" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="D1" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="J1" s="6"/>
+    </row>
+    <row r="2" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A2" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F2" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="G2" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="H2" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="I2" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="J2" s="11"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A3" s="12"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="15"/>
+    </row>
+    <row r="4" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A4" s="12"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="H4" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="I4" s="16" t="s">
+        <v>76</v>
+      </c>
+      <c r="J4" s="11"/>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A5" s="12"/>
+      <c r="B5" s="13"/>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="14"/>
+      <c r="G5" s="14"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="15"/>
+    </row>
+    <row r="6" spans="1:10" ht="409.6" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="17"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="G6" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="H6" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="I6" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="J6" s="11"/>
+    </row>
+    <row r="7" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A7" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>87</v>
+      </c>
+      <c r="E7" s="9" t="s">
+        <v>88</v>
+      </c>
+      <c r="F7" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="H7" s="10"/>
+      <c r="I7" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="J7" s="11"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A8" s="12"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="14"/>
+      <c r="D8" s="14"/>
+      <c r="E8" s="14"/>
+      <c r="F8" s="14"/>
+      <c r="G8" s="14"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="15"/>
+    </row>
+    <row r="9" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A9" s="12"/>
+      <c r="B9" s="13"/>
+      <c r="C9" s="21" t="s">
+        <v>92</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>94</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="G9" s="21" t="s">
+        <v>96</v>
+      </c>
+      <c r="H9" s="21" t="s">
+        <v>97</v>
+      </c>
+      <c r="I9" s="16" t="s">
+        <v>98</v>
+      </c>
+      <c r="J9" s="11"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A10" s="12"/>
+      <c r="B10" s="13"/>
+      <c r="C10" s="14"/>
+      <c r="D10" s="14"/>
+      <c r="E10" s="14"/>
+      <c r="F10" s="14"/>
+      <c r="G10" s="14"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="15"/>
+    </row>
+    <row r="11" spans="1:10" ht="409.6" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="17"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="D11" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="E11" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="G11" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="H11" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="I11" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="J11" s="11"/>
+    </row>
+    <row r="12" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A12" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>107</v>
+      </c>
+      <c r="C12" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="D12" s="9" t="s">
         <v>109</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="E12" s="9" t="s">
         <v>110</v>
       </c>
-      <c r="H1" s="8" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>106</v>
-      </c>
-      <c r="C2" s="9">
-        <v>3</v>
-      </c>
-      <c r="D2" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="F2" t="s">
-        <v>61</v>
-      </c>
-      <c r="G2">
-        <v>3</v>
-      </c>
-      <c r="H2" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="I2" s="5"/>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="9"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="F3" t="s">
-        <v>61</v>
-      </c>
-      <c r="G3">
-        <v>3</v>
-      </c>
-      <c r="H3" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="I3" s="5"/>
-    </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="9"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" t="s">
-        <v>65</v>
-      </c>
-      <c r="F4" t="s">
-        <v>61</v>
-      </c>
-      <c r="G4">
-        <v>15</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="I4" s="5"/>
-    </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="9" t="s">
-        <v>105</v>
-      </c>
-      <c r="B5" s="9" t="s">
-        <v>107</v>
-      </c>
-      <c r="C5" s="9">
-        <v>3</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="E5" t="s">
-        <v>68</v>
-      </c>
-      <c r="F5" t="s">
-        <v>61</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="I5" s="5"/>
-    </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="9"/>
-      <c r="B6" s="9"/>
-      <c r="C6" s="9"/>
-      <c r="D6" s="9"/>
-      <c r="E6" t="s">
-        <v>70</v>
-      </c>
-      <c r="F6" t="s">
-        <v>61</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6" s="5" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C7" s="9">
-        <v>1</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>73</v>
-      </c>
-      <c r="E7" t="s">
-        <v>74</v>
-      </c>
-      <c r="F7" t="s">
-        <v>75</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7" s="5" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="9"/>
-      <c r="B8" s="9"/>
-      <c r="C8" s="9"/>
-      <c r="D8" s="9"/>
-      <c r="E8" t="s">
-        <v>77</v>
-      </c>
-      <c r="F8" t="s">
-        <v>78</v>
-      </c>
-      <c r="G8">
-        <v>1</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" t="s">
-        <v>80</v>
-      </c>
-      <c r="F9" t="s">
-        <v>78</v>
-      </c>
-      <c r="G9">
-        <v>1</v>
-      </c>
-      <c r="H9" s="5" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="B10" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="C10" s="9">
-        <v>1</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="E10" t="s">
-        <v>83</v>
-      </c>
-      <c r="F10" t="s">
-        <v>78</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="9"/>
-      <c r="B11" s="9"/>
-      <c r="C11" s="9"/>
-      <c r="D11" s="9"/>
-      <c r="E11" t="s">
-        <v>85</v>
-      </c>
-      <c r="F11" t="s">
-        <v>86</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-      <c r="H11" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
-      <c r="A12" s="9"/>
-      <c r="B12" s="9"/>
-      <c r="C12" s="9"/>
-      <c r="D12" s="9"/>
-      <c r="E12" t="s">
-        <v>88</v>
-      </c>
-      <c r="F12" t="s">
-        <v>86</v>
-      </c>
-      <c r="G12">
-        <v>1</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
-      <c r="A13" s="9" t="s">
-        <v>43</v>
-      </c>
-      <c r="B13" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="C13" s="9">
-        <v>1</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>90</v>
-      </c>
-      <c r="E13" t="s">
-        <v>91</v>
-      </c>
-      <c r="F13" t="s">
-        <v>78</v>
-      </c>
-      <c r="G13">
-        <v>1</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
-      <c r="A14" s="9"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="9"/>
-      <c r="E14" t="s">
-        <v>93</v>
-      </c>
-      <c r="F14" t="s">
-        <v>78</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
-      <c r="A15" s="9"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="9"/>
-      <c r="E15" t="s">
-        <v>95</v>
-      </c>
-      <c r="F15" t="s">
-        <v>78</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
-      <c r="A16" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" s="9" t="s">
-        <v>36</v>
-      </c>
-      <c r="C16" s="9">
-        <v>1</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>97</v>
-      </c>
-      <c r="E16" t="s">
-        <v>98</v>
-      </c>
-      <c r="F16" t="s">
-        <v>75</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
-      </c>
-      <c r="H16" s="4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="9"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
+      <c r="G12" s="9" t="s">
+        <v>111</v>
+      </c>
+      <c r="H12" s="9"/>
+      <c r="I12" s="10" t="s">
+        <v>112</v>
+      </c>
+      <c r="J12" s="11"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A13" s="12"/>
+      <c r="B13" s="13"/>
+      <c r="C13" s="14"/>
+      <c r="D13" s="14"/>
+      <c r="E13" s="14"/>
+      <c r="F13" s="14"/>
+      <c r="G13" s="14"/>
+      <c r="H13" s="14"/>
+      <c r="I13" s="14"/>
+      <c r="J13" s="15"/>
+    </row>
+    <row r="14" spans="1:10" ht="120" x14ac:dyDescent="0.2">
+      <c r="A14" s="12"/>
+      <c r="B14" s="13"/>
+      <c r="C14" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16" t="s">
+        <v>114</v>
+      </c>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="H14" s="16" t="s">
+        <v>116</v>
+      </c>
+      <c r="I14" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="J14" s="11"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A15" s="12"/>
+      <c r="B15" s="13"/>
+      <c r="C15" s="14"/>
+      <c r="D15" s="14"/>
+      <c r="E15" s="14"/>
+      <c r="F15" s="14"/>
+      <c r="G15" s="14"/>
+      <c r="H15" s="14"/>
+      <c r="I15" s="14"/>
+      <c r="J15" s="15"/>
+    </row>
+    <row r="16" spans="1:10" ht="409.6" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="17"/>
+      <c r="B16" s="18"/>
+      <c r="C16" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="D16" s="22" t="s">
+        <v>119</v>
+      </c>
+      <c r="E16" s="19" t="s">
+        <v>120</v>
+      </c>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="H16" s="19"/>
+      <c r="I16" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="J16" s="11"/>
+    </row>
+    <row r="17" spans="1:10" ht="90" x14ac:dyDescent="0.2">
+      <c r="A17" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>125</v>
+      </c>
       <c r="D17" s="9"/>
-      <c r="E17" t="s">
-        <v>100</v>
-      </c>
-      <c r="F17" t="s">
-        <v>101</v>
-      </c>
-      <c r="G17">
-        <v>1</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="9"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" t="s">
-        <v>103</v>
-      </c>
-      <c r="F18" t="s">
-        <v>78</v>
-      </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="I19" s="7"/>
-      <c r="J19" s="5"/>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="I20" s="7"/>
-      <c r="J20" s="4"/>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="I21" s="7"/>
-      <c r="J21" s="4"/>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="I24" s="7"/>
-      <c r="J24" s="4"/>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="I25" s="7"/>
-      <c r="J25" s="4"/>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="I26" s="7"/>
-      <c r="J26" s="4"/>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="J29" s="4"/>
-    </row>
-    <row r="30" spans="1:10">
-      <c r="I30" s="7"/>
-      <c r="J30" s="4"/>
-    </row>
-    <row r="31" spans="1:10">
-      <c r="I31" s="7"/>
-      <c r="J31" s="4"/>
+      <c r="E17" s="10" t="s">
+        <v>126</v>
+      </c>
+      <c r="F17" s="10"/>
+      <c r="G17" s="10" t="s">
+        <v>127</v>
+      </c>
+      <c r="H17" s="10"/>
+      <c r="I17" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="J17" s="11"/>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A18" s="12"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="15"/>
+    </row>
+    <row r="19" spans="1:10" ht="75" x14ac:dyDescent="0.2">
+      <c r="A19" s="12"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="16" t="s">
+        <v>129</v>
+      </c>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16" t="s">
+        <v>130</v>
+      </c>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16" t="s">
+        <v>132</v>
+      </c>
+      <c r="J19" s="11"/>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A20" s="12"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="14"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="15"/>
+    </row>
+    <row r="21" spans="1:10" ht="76" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="17"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="19" t="s">
+        <v>133</v>
+      </c>
+      <c r="D21" s="19"/>
+      <c r="E21" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="F21" s="22"/>
+      <c r="G21" s="19" t="s">
+        <v>135</v>
+      </c>
+      <c r="H21" s="19"/>
+      <c r="I21" s="19" t="s">
+        <v>136</v>
+      </c>
+      <c r="J21" s="11"/>
+    </row>
+    <row r="22" spans="1:10" ht="75" x14ac:dyDescent="0.2">
+      <c r="A22" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>139</v>
+      </c>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9" t="s">
+        <v>140</v>
+      </c>
+      <c r="F22" s="9"/>
+      <c r="G22" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="H22" s="10"/>
+      <c r="I22" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="J22" s="11"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A23" s="12"/>
+      <c r="B23" s="13"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="15"/>
+    </row>
+    <row r="24" spans="1:10" ht="60" x14ac:dyDescent="0.2">
+      <c r="A24" s="12"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="16" t="s">
+        <v>143</v>
+      </c>
+      <c r="D24" s="16"/>
+      <c r="E24" s="16" t="s">
+        <v>144</v>
+      </c>
+      <c r="F24" s="16"/>
+      <c r="G24" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="H24" s="16"/>
+      <c r="I24" s="16" t="s">
+        <v>146</v>
+      </c>
+      <c r="J24" s="11"/>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A25" s="12"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="15"/>
+    </row>
+    <row r="26" spans="1:10" ht="46" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="17"/>
+      <c r="B26" s="18"/>
+      <c r="C26" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="D26" s="19"/>
+      <c r="E26" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="F26" s="19"/>
+      <c r="G26" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="H26" s="19"/>
+      <c r="I26" s="19" t="s">
+        <v>150</v>
+      </c>
+      <c r="J26" s="11"/>
+    </row>
+    <row r="27" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A27" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>153</v>
+      </c>
+      <c r="E27" s="10" t="s">
+        <v>154</v>
+      </c>
+      <c r="F27" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="H27" s="10"/>
+      <c r="I27" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="J27" s="11"/>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A28" s="12"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="14"/>
+      <c r="J28" s="15"/>
+    </row>
+    <row r="29" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A29" s="12"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="16" t="s">
+        <v>158</v>
+      </c>
+      <c r="D29" s="16"/>
+      <c r="E29" s="16" t="s">
+        <v>159</v>
+      </c>
+      <c r="F29" s="16" t="s">
+        <v>160</v>
+      </c>
+      <c r="G29" s="16" t="s">
+        <v>161</v>
+      </c>
+      <c r="H29" s="16"/>
+      <c r="I29" s="16" t="s">
+        <v>162</v>
+      </c>
+      <c r="J29" s="11"/>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A30" s="12"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="15"/>
+    </row>
+    <row r="31" spans="1:10" ht="409.6" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="17"/>
+      <c r="B31" s="18"/>
+      <c r="C31" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="D31" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="E31" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="F31" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="G31" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="H31" s="19"/>
+      <c r="I31" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="J31" s="11"/>
+    </row>
+    <row r="32" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A32" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>171</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>172</v>
+      </c>
+      <c r="E32" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="F32" s="9" t="s">
+        <v>174</v>
+      </c>
+      <c r="G32" s="9" t="s">
+        <v>175</v>
+      </c>
+      <c r="H32" s="9" t="s">
+        <v>176</v>
+      </c>
+      <c r="I32" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="J32" s="23" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A33" s="12"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="14"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
+      <c r="H33" s="14"/>
+      <c r="I33" s="14"/>
+      <c r="J33" s="15"/>
+    </row>
+    <row r="34" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A34" s="12"/>
+      <c r="B34" s="13"/>
+      <c r="C34" s="16" t="s">
+        <v>179</v>
+      </c>
+      <c r="D34" s="16" t="s">
+        <v>180</v>
+      </c>
+      <c r="E34" s="16" t="s">
+        <v>181</v>
+      </c>
+      <c r="F34" s="16" t="s">
+        <v>182</v>
+      </c>
+      <c r="G34" s="16" t="s">
+        <v>183</v>
+      </c>
+      <c r="H34" s="16" t="s">
+        <v>184</v>
+      </c>
+      <c r="I34" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="J34" s="11"/>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A35" s="12"/>
+      <c r="B35" s="13"/>
+      <c r="C35" s="14"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
+      <c r="H35" s="14"/>
+      <c r="I35" s="14"/>
+      <c r="J35" s="15"/>
+    </row>
+    <row r="36" spans="1:10" ht="409.6" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A36" s="17"/>
+      <c r="B36" s="18"/>
+      <c r="C36" s="19" t="s">
+        <v>186</v>
+      </c>
+      <c r="D36" s="19" t="s">
+        <v>187</v>
+      </c>
+      <c r="E36" s="19" t="s">
+        <v>188</v>
+      </c>
+      <c r="F36" s="19" t="s">
+        <v>189</v>
+      </c>
+      <c r="G36" s="19" t="s">
+        <v>190</v>
+      </c>
+      <c r="H36" s="19"/>
+      <c r="I36" s="19" t="s">
+        <v>191</v>
+      </c>
+      <c r="J36" s="11" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A37" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="C37" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="D37" s="9" t="s">
+        <v>196</v>
+      </c>
+      <c r="E37" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="F37" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="G37" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="H37" s="10"/>
+      <c r="I37" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="J37" s="11"/>
+    </row>
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A38" s="12"/>
+      <c r="B38" s="13"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="14"/>
+      <c r="G38" s="14"/>
+      <c r="H38" s="14"/>
+      <c r="I38" s="14"/>
+      <c r="J38" s="15"/>
+    </row>
+    <row r="39" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A39" s="12"/>
+      <c r="B39" s="13"/>
+      <c r="C39" s="16" t="s">
+        <v>201</v>
+      </c>
+      <c r="D39" s="16" t="s">
+        <v>202</v>
+      </c>
+      <c r="E39" s="16" t="s">
+        <v>203</v>
+      </c>
+      <c r="F39" s="16" t="s">
+        <v>204</v>
+      </c>
+      <c r="G39" s="16" t="s">
+        <v>205</v>
+      </c>
+      <c r="H39" s="16" t="s">
+        <v>206</v>
+      </c>
+      <c r="I39" s="16" t="s">
+        <v>207</v>
+      </c>
+      <c r="J39" s="11" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10" ht="165" x14ac:dyDescent="0.2">
+      <c r="A40" s="12"/>
+      <c r="B40" s="13"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="14"/>
+      <c r="F40" s="14"/>
+      <c r="G40" s="14"/>
+      <c r="H40" s="14"/>
+      <c r="I40" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="J40" s="11" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10" ht="409.6" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A41" s="17"/>
+      <c r="B41" s="18"/>
+      <c r="C41" s="19" t="s">
+        <v>211</v>
+      </c>
+      <c r="D41" s="19" t="s">
+        <v>212</v>
+      </c>
+      <c r="E41" s="19" t="s">
+        <v>213</v>
+      </c>
+      <c r="F41" s="19"/>
+      <c r="G41" s="19" t="s">
+        <v>214</v>
+      </c>
+      <c r="H41" s="19" t="s">
+        <v>215</v>
+      </c>
+      <c r="I41" s="19" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A42" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="B42" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>219</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="E42" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="F42" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="G42" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="H42" s="20" t="s">
+        <v>224</v>
+      </c>
+      <c r="I42" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="J42" s="11"/>
+    </row>
+    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A43" s="12"/>
+      <c r="B43" s="13"/>
+      <c r="C43" s="14"/>
+      <c r="D43" s="14"/>
+      <c r="E43" s="14"/>
+      <c r="F43" s="14"/>
+      <c r="G43" s="14"/>
+      <c r="H43" s="14"/>
+      <c r="I43" s="14"/>
+      <c r="J43" s="15"/>
+    </row>
+    <row r="44" spans="1:10" ht="409.6" x14ac:dyDescent="0.2">
+      <c r="A44" s="12"/>
+      <c r="B44" s="13"/>
+      <c r="C44" s="16" t="s">
+        <v>226</v>
+      </c>
+      <c r="D44" s="16" t="s">
+        <v>227</v>
+      </c>
+      <c r="E44" s="16" t="s">
+        <v>228</v>
+      </c>
+      <c r="F44" s="16" t="s">
+        <v>229</v>
+      </c>
+      <c r="G44" s="16" t="s">
+        <v>230</v>
+      </c>
+      <c r="H44" s="16"/>
+      <c r="I44" s="16" t="s">
+        <v>231</v>
+      </c>
+      <c r="J44" s="11" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A45" s="12"/>
+      <c r="B45" s="13"/>
+      <c r="C45" s="14"/>
+      <c r="D45" s="14"/>
+      <c r="E45" s="14"/>
+      <c r="F45" s="14"/>
+      <c r="G45" s="14"/>
+      <c r="H45" s="14"/>
+      <c r="I45" s="14"/>
+      <c r="J45" s="15"/>
+    </row>
+    <row r="46" spans="1:10" ht="409.6" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="17"/>
+      <c r="B46" s="18"/>
+      <c r="C46" s="19" t="s">
+        <v>233</v>
+      </c>
+      <c r="D46" s="19" t="s">
+        <v>234</v>
+      </c>
+      <c r="E46" s="19" t="s">
+        <v>235</v>
+      </c>
+      <c r="F46" s="19" t="s">
+        <v>236</v>
+      </c>
+      <c r="G46" s="19" t="s">
+        <v>237</v>
+      </c>
+      <c r="H46" s="19" t="s">
+        <v>238</v>
+      </c>
+      <c r="I46" s="19" t="s">
+        <v>239</v>
+      </c>
+      <c r="J46" s="11"/>
     </row>
   </sheetData>
-  <mergeCells count="24">
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="B13:B15"/>
-    <mergeCell ref="C13:C15"/>
-    <mergeCell ref="D13:D15"/>
-    <mergeCell ref="A16:A18"/>
-    <mergeCell ref="B16:B18"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="C16:C18"/>
-    <mergeCell ref="A7:A9"/>
-    <mergeCell ref="B7:B9"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="D7:D9"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="B10:B12"/>
-    <mergeCell ref="C10:C12"/>
-    <mergeCell ref="D10:D12"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="C5:C6"/>
-    <mergeCell ref="D5:D6"/>
+  <mergeCells count="18">
+    <mergeCell ref="A37:A41"/>
+    <mergeCell ref="B37:B41"/>
+    <mergeCell ref="A42:A46"/>
+    <mergeCell ref="B42:B46"/>
+    <mergeCell ref="A22:A26"/>
+    <mergeCell ref="B22:B26"/>
+    <mergeCell ref="A27:A31"/>
+    <mergeCell ref="B27:B31"/>
+    <mergeCell ref="A32:A36"/>
+    <mergeCell ref="B32:B36"/>
+    <mergeCell ref="A2:A6"/>
+    <mergeCell ref="B2:B6"/>
+    <mergeCell ref="A7:A11"/>
+    <mergeCell ref="B7:B11"/>
+    <mergeCell ref="A12:A16"/>
+    <mergeCell ref="B12:B16"/>
+    <mergeCell ref="A17:A21"/>
+    <mergeCell ref="B17:B21"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="H2" r:id="rId1" display="https://www.amazon.in/Cleanse-Natural-Protection-Hydration-Refreshed/dp/B0DNF54WB1/ref=sr_1_2_sspa?crid=1KH12Y9SG8OIN&amp;dib=eyJ2IjoiMSJ9.Iwh0-03nxc_1RvtDc0hQ4gumLXDqdVUIhJRp8Wz--3DzBI4S0tJ2OebvR_wWripVjyW7u3eflgSpJCcTtno14ojMUfi883DS397EfrOmKwUIo9PVPAmhB-NvgcHpDp5fkeboGNyzuYrk5moG-fmbJJGyrc-A-Ek8RtM2xIZqrhYeDwoAsn3o0qmiN4UPa79CXsu0FOsaoRNRQInRnfkHn_7-MfgSCGfJh2E7p1LdOeubYebJARuMF6G6wiX1o-O6GUQU1oTHHfg1-QTyObuVxRxhXgyGHoaDM9S9N1drRUE.Q16g2USIdRzicbqek9FsZ0FtlznnL2eyArs6eebfuZs&amp;dib_tag=se&amp;keywords=aloe%2Bvera%2Bneem%2Bsoap&amp;qid=1770440771&amp;sprefix=aloe%2Bvera%2Bnee%2Bsoap%2Caps%2C533&amp;sr=8-2-spons&amp;aref=nNldu59BBf&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1" xr:uid="{0F986C67-C469-8B4C-977B-BD945D66E81F}"/>
-    <hyperlink ref="H3" r:id="rId2" display="https://www.amazon.in/JIVTARA-Neem-Aloe-Vera-Ayurvedic/dp/B0FRSH67NR/ref=sr_1_8?crid=1KH12Y9SG8OIN&amp;dib=eyJ2IjoiMSJ9.Iwh0-03nxc_1RvtDc0hQ4gumLXDqdVUIhJRp8Wz--3DzBI4S0tJ2OebvR_wWripVjyW7u3eflgSpJCcTtno14ojMUfi883DS397EfrOmKwUIo9PVPAmhB-NvgcHpDp5fkeboGNyzuYrk5moG-fmbJJGyrc-A-Ek8RtM2xIZqrhYeDwoAsn3o0qmiN4UPa79CXsu0FOsaoRNRQInRnfkHn_7-MfgSCGfJh2E7p1LdOeubYebJARuMF6G6wiX1o-O6GUQU1oTHHfg1-QTyObuVxRxhXgyGHoaDM9S9N1drRUE.Q16g2USIdRzicbqek9FsZ0FtlznnL2eyArs6eebfuZs&amp;dib_tag=se&amp;keywords=aloe+vera+neem+soap&amp;qid=1770440771&amp;sprefix=aloe+vera+nee+soap%2Caps%2C533&amp;sr=8-8" xr:uid="{191ABC7F-1ABC-6949-A10C-CB0A5EE8B195}"/>
-    <hyperlink ref="H4" r:id="rId3" display="https://www.amazon.in/Neem-Aloe-Nourishing-Anti-Aging-Younger-Looking/dp/B0GGZ7VFQY/ref=sr_1_2_sspa?crid=VPIRKYRAJFJO&amp;dib=eyJ2IjoiMSJ9.9uHpevtJsPOCTBp8e1y2EEhgLYHAp2E5VCHHstWg7cGYof6pn9SIq7Xw19C2pB2df-yi3MrJ083iC71UOfEqzpK-52ew9V3wNJ320Lzy-nCI7q2G6xgLpPht8CCCqzL7OkNl4W-B9cV1LdM7-x9M54luvSyFIhffDyi6DmotRN2a8s7x3bqkHAnrXA8uRREQRkxDglWWb70Ct3wCltmhnOoqiaJnYoz-3dFfpU-V4J7G4PYzjsI5GdgbSr4YjH5JcCRmzQAbUNyRt23SnSVDDzwJuYXuhzUlyBAuIg_1cYg.3_hp__FC6apmrrawqCesUU72SkbjBKGUTrrUE6j18ls&amp;dib_tag=se&amp;keywords=aloe%2Bvera%2Bneem%2Bsoap&amp;qid=1770440895&amp;s=beauty&amp;sprefix=aloe%2Bvera%2Bneem%2Bsoap%2Cbeauty%2C353&amp;sr=1-2-spons&amp;aref=BOLlnmOWjQ&amp;sp_csd=d2lkZ2V0TmFtZT1zcF9hdGY&amp;th=1" xr:uid="{69FC3F55-FB71-4A47-A3AE-4C13FC9753E3}"/>
-    <hyperlink ref="H5" r:id="rId4" xr:uid="{CEA3A087-C57D-A846-98C0-CA0902501E1D}"/>
-    <hyperlink ref="H6" r:id="rId5" xr:uid="{D0C779CC-D2CB-5C45-BC0D-2F7F1F287031}"/>
-    <hyperlink ref="H7" r:id="rId6" xr:uid="{16800EFD-2848-F74C-9968-B05601E33F2D}"/>
-    <hyperlink ref="H8" r:id="rId7" xr:uid="{B8EE2580-B367-724A-9831-839333F73722}"/>
-    <hyperlink ref="H9" r:id="rId8" xr:uid="{99B7E49A-15E6-734B-B3A7-94C36248905A}"/>
-    <hyperlink ref="H10" r:id="rId9" xr:uid="{1F929B43-E253-F849-B07C-E7AA96D247AB}"/>
+    <hyperlink ref="J32" r:id="rId1" xr:uid="{C1AA09B6-7279-C24E-AF3E-DA86CD96B881}"/>
+    <hyperlink ref="H42" r:id="rId2" xr:uid="{F7AE3BB7-AB5B-C440-817A-94DF2255A4F7}"/>
+    <hyperlink ref="F7" r:id="rId3" display="https://www.flipkart.com/yardley-london-english-lavender-90-naturally-derived-daily-bathing-luxury-soap-women/p/itm0fc388db1559c?pid=SOPEU6NPU9MYJFMS&amp;lid=LSTSOPEU6NPU9MYJFMSETQQHW&amp;marketplace=FLIPKART&amp;q=yardley+luxury+soap&amp;store=g9b%2F5nz%2Fb1b%2Fyug&amp;srno=s_1_2&amp;otracker=search&amp;otracker1=search&amp;fm=Search&amp;iid=177dacc7-1a06-4fd3-bceb-2e35901c841c.SOPEU6NPU9MYJFMS.SEARCH&amp;ppt=sp&amp;ppn=sp&amp;ssid=qj91hzqmkg0000001772555554054&amp;qH=ab1717523daf7c78&amp;ov_redirect=true&amp;ov_redirect=true" xr:uid="{7BAC8061-08B3-8042-863C-D1CB6D745CFF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
